--- a/생활속의통계/Excel/4주차 실습데이터.xlsx
+++ b/생활속의통계/Excel/4주차 실습데이터.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DD\성서대\생활 속의 통계\2025-2\4주차(9월25일)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KBS\Desktop\hayeun\26_2_myLecture\생활속의통계\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F113BC95-FB67-42EE-AED3-8932F3BFE13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A28B468-41FC-4C71-A0C0-5FA3DB7FE9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="15600" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="예제 1" sheetId="29" r:id="rId1"/>
@@ -31,9 +31,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -326,7 +323,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -360,9 +357,6 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -375,13 +369,10 @@
     <xf numFmtId="41" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -690,16 +681,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165FB6B9-7C69-464C-BCBE-5F21B58C371B}">
   <dimension ref="A2:E8"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" customWidth="1"/>
-    <col min="2" max="2" width="10.09765625" customWidth="1"/>
-    <col min="3" max="3" width="13.09765625" customWidth="1"/>
-    <col min="4" max="4" width="12.796875" customWidth="1"/>
-    <col min="5" max="5" width="10.296875" customWidth="1"/>
+    <col min="1" max="1" width="12.125" customWidth="1"/>
+    <col min="2" max="2" width="10.125" customWidth="1"/>
+    <col min="3" max="3" width="13.125" customWidth="1"/>
+    <col min="4" max="4" width="12.75" customWidth="1"/>
+    <col min="5" max="5" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>25</v>
       </c>
@@ -713,62 +704,98 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" s="2">
         <v>0.05</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C3" s="6">
+        <f>A3*B3</f>
+        <v>0.05</v>
+      </c>
+      <c r="D3" s="6">
+        <f>A3*A3*B3</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2</v>
       </c>
       <c r="B4" s="2">
         <v>0.25</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C4" s="6">
+        <f t="shared" ref="C4:C7" si="0">A4*B4</f>
+        <v>0.5</v>
+      </c>
+      <c r="D4" s="6">
+        <f t="shared" ref="D4:D7" si="1">A4*A4*B4</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>3</v>
       </c>
       <c r="B5" s="2">
         <v>0.4</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C5" s="6">
+        <f t="shared" si="0"/>
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="D5" s="6">
+        <f t="shared" si="1"/>
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>4</v>
       </c>
       <c r="B6" s="2">
         <v>0.25</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C6" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D6" s="6">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>5</v>
       </c>
       <c r="B7" s="2">
         <v>0.05</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C7" s="6">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+      <c r="D7" s="6">
+        <f t="shared" si="1"/>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
+      <c r="C8" s="6">
+        <f>SUM(C3:C7)</f>
+        <v>3</v>
+      </c>
+      <c r="D8" s="6">
+        <f>SUM(D3:D7)-C8^2</f>
+        <v>0.90000000000000036</v>
+      </c>
       <c r="E8" t="s">
         <v>35</v>
       </c>
@@ -782,16 +809,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D639BFA-CD79-4560-BD63-78E4B22C7495}">
   <dimension ref="A2:E8"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" customWidth="1"/>
-    <col min="2" max="2" width="10.19921875" customWidth="1"/>
-    <col min="3" max="3" width="13.19921875" customWidth="1"/>
-    <col min="4" max="4" width="21.796875" customWidth="1"/>
-    <col min="5" max="5" width="10.19921875" customWidth="1"/>
+    <col min="1" max="1" width="12.125" customWidth="1"/>
+    <col min="2" max="2" width="10.25" customWidth="1"/>
+    <col min="3" max="3" width="13.25" customWidth="1"/>
+    <col min="4" max="4" width="21.75" customWidth="1"/>
+    <col min="5" max="5" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>25</v>
       </c>
@@ -805,7 +832,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -819,7 +846,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -833,7 +860,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -847,7 +874,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -861,7 +888,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -875,8 +902,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B8" s="11" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
         <v>36</v>
       </c>
       <c r="C8" s="5" t="s">
@@ -898,76 +925,76 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{452F4B6B-88FA-4D6A-87DB-7C144118402A}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="16.09765625" customWidth="1"/>
-    <col min="4" max="4" width="19.19921875" customWidth="1"/>
-    <col min="5" max="5" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.296875" customWidth="1"/>
+    <col min="3" max="3" width="16.125" customWidth="1"/>
+    <col min="4" max="4" width="19.25" customWidth="1"/>
+    <col min="5" max="5" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>0.25</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>-5000000</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="12">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" s="12" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="11">
         <v>0.5</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="12">
         <v>2000000</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="12">
         <v>2500000</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="12" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="11">
         <v>0.25</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="12">
         <v>10000000</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>5000000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -984,67 +1011,67 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="1">
         <v>0.25</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="13">
         <v>-5000000</v>
       </c>
-      <c r="D8" s="15"/>
+      <c r="D8" s="14"/>
       <c r="E8" s="6"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B9" s="1">
         <v>0.5</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="13">
         <v>2000000</v>
       </c>
-      <c r="D9" s="15"/>
+      <c r="D9" s="14"/>
       <c r="E9" s="6"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="1">
         <v>0.25</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="13">
         <v>10000000</v>
       </c>
-      <c r="D10" s="15"/>
+      <c r="D10" s="14"/>
       <c r="E10" s="6"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
       <c r="F11" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="D12" s="18"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="D13" s="18"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D12" s="16"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D13" s="16"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -1061,60 +1088,60 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B17" s="1">
         <v>0.25</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="13">
         <v>-1000000</v>
       </c>
-      <c r="D17" s="15"/>
+      <c r="D17" s="14"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B18" s="1">
         <v>0.5</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="13">
         <v>2500000</v>
       </c>
-      <c r="D18" s="15"/>
+      <c r="D18" s="14"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B19" s="1">
         <v>0.25</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="13">
         <v>5000000</v>
       </c>
-      <c r="D19" s="15"/>
+      <c r="D19" s="14"/>
       <c r="E19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
       <c r="F20" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="D21" s="18"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="D22" s="18"/>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D21" s="16"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D22" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1126,76 +1153,76 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B54E7F93-CF65-4DAA-B3EB-6DBD31CBAB62}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="16.09765625" customWidth="1"/>
-    <col min="4" max="4" width="19.19921875" customWidth="1"/>
-    <col min="5" max="5" width="22.796875" customWidth="1"/>
-    <col min="6" max="6" width="13.796875" customWidth="1"/>
+    <col min="3" max="3" width="16.125" customWidth="1"/>
+    <col min="4" max="4" width="19.25" customWidth="1"/>
+    <col min="5" max="5" width="22.75" customWidth="1"/>
+    <col min="6" max="6" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>0.25</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>-5000000</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="12">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" s="12" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="11">
         <v>0.5</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="12">
         <v>2000000</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="12">
         <v>2500000</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="12" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="11">
         <v>0.25</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="12">
         <v>10000000</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>5000000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -1212,7 +1239,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1229,7 +1256,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1246,7 +1273,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1263,7 +1290,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>36</v>
       </c>
@@ -1277,20 +1304,18 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="C12" s="16"/>
-      <c r="D12" s="17"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="C13" s="16"/>
-      <c r="D13" s="17"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D12" s="15"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D13" s="15"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -1307,7 +1332,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
@@ -1324,7 +1349,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -1341,7 +1366,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>6</v>
       </c>
@@ -1358,7 +1383,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
         <v>36</v>
       </c>
@@ -1380,16 +1405,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{948DC152-A0E4-4F0A-AF32-70B901E1C395}">
-  <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="16.09765625" customWidth="1"/>
-    <col min="4" max="4" width="19.19921875" customWidth="1"/>
-    <col min="5" max="5" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.19921875" customWidth="1"/>
+    <col min="3" max="3" width="16.125" customWidth="1"/>
+    <col min="4" max="4" width="19.25" customWidth="1"/>
+    <col min="5" max="5" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1403,7 +1428,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1417,7 +1442,7 @@
         <v>-2000000</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1431,7 +1456,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1445,12 +1470,12 @@
         <v>7000000</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -1467,7 +1492,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1480,7 +1505,7 @@
       <c r="D8" s="7"/>
       <c r="E8" s="5"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1494,7 +1519,7 @@
       <c r="E9" s="5"/>
       <c r="J9" s="10"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1507,7 +1532,7 @@
       <c r="D10" s="7"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>36</v>
       </c>
@@ -1517,18 +1542,18 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="D12" s="17"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="D13" s="17"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D12" s="15"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D13" s="15"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -1545,7 +1570,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
@@ -1558,7 +1583,7 @@
       <c r="D17" s="7"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -1571,7 +1596,7 @@
       <c r="D18" s="7"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>6</v>
       </c>
@@ -1584,7 +1609,7 @@
       <c r="D19" s="7"/>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
         <v>36</v>
       </c>
@@ -1594,17 +1619,11 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="C21" s="16"/>
-      <c r="D21" s="17"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D21" s="15"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D22" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1615,16 +1634,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3661351A-B14A-435E-B895-7FEBFE7BB31A}">
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="16.09765625" customWidth="1"/>
-    <col min="4" max="4" width="19.19921875" customWidth="1"/>
-    <col min="5" max="5" width="21.796875" customWidth="1"/>
-    <col min="6" max="6" width="11.296875" customWidth="1"/>
+    <col min="3" max="3" width="16.125" customWidth="1"/>
+    <col min="4" max="4" width="19.25" customWidth="1"/>
+    <col min="5" max="5" width="21.75" customWidth="1"/>
+    <col min="6" max="6" width="11.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1638,7 +1657,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1652,7 +1671,7 @@
         <v>-2000000</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1666,7 +1685,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1680,12 +1699,12 @@
         <v>7000000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -1702,7 +1721,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1719,7 +1738,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1736,7 +1755,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1753,7 +1772,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>36</v>
       </c>
@@ -1767,20 +1786,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="C12" s="16"/>
-      <c r="D12" s="17"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="C13" s="16"/>
-      <c r="D13" s="17"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D12" s="15"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D13" s="15"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -1797,7 +1814,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
@@ -1814,7 +1831,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -1831,7 +1848,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>6</v>
       </c>
@@ -1848,7 +1865,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
         <v>36</v>
       </c>
@@ -1862,14 +1879,11 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="D21" s="17"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="D22" s="17"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="D23" s="16"/>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D21" s="15"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D22" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/생활속의통계/Excel/4주차 실습데이터.xlsx
+++ b/생활속의통계/Excel/4주차 실습데이터.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KBS\Desktop\hayeun\26_2_myLecture\생활속의통계\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A28B468-41FC-4C71-A0C0-5FA3DB7FE9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A1B588-E5BA-4563-B2FD-74B078FA6293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="예제 1" sheetId="29" r:id="rId1"/>
@@ -681,7 +681,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165FB6B9-7C69-464C-BCBE-5F21B58C371B}">
   <dimension ref="A2:E8"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -690,7 +690,7 @@
     <col min="5" max="5" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A2" s="2" t="s">
         <v>25</v>
       </c>
@@ -704,7 +704,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -720,7 +720,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -736,7 +736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -752,7 +752,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -768,7 +768,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -784,7 +784,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.6">
       <c r="B8" t="s">
         <v>44</v>
       </c>
@@ -809,7 +809,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D639BFA-CD79-4560-BD63-78E4B22C7495}">
   <dimension ref="A2:E8"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
     <col min="2" max="2" width="10.25" customWidth="1"/>
@@ -818,7 +818,7 @@
     <col min="5" max="5" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A2" s="2" t="s">
         <v>25</v>
       </c>
@@ -832,7 +832,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -846,7 +846,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -860,7 +860,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -874,7 +874,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -888,7 +888,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -902,7 +902,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.6">
       <c r="B8" t="s">
         <v>36</v>
       </c>
@@ -925,15 +925,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{452F4B6B-88FA-4D6A-87DB-7C144118402A}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="3" max="3" width="16.125" customWidth="1"/>
     <col min="4" max="4" width="19.25" customWidth="1"/>
-    <col min="5" max="5" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -947,7 +947,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A2" s="11" t="s">
         <v>4</v>
       </c>
@@ -961,7 +961,7 @@
         <v>-1000000</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A3" s="11" t="s">
         <v>5</v>
       </c>
@@ -975,7 +975,7 @@
         <v>2500000</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A4" s="11" t="s">
         <v>6</v>
       </c>
@@ -989,12 +989,12 @@
         <v>5000000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -1011,7 +1011,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1021,10 +1021,16 @@
       <c r="C8" s="13">
         <v>-5000000</v>
       </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="6"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D8" s="14">
+        <f>B8*C8</f>
+        <v>-1250000</v>
+      </c>
+      <c r="E8" s="6">
+        <f>B8*C8*C8</f>
+        <v>6250000000000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1034,10 +1040,16 @@
       <c r="C9" s="13">
         <v>2000000</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="6"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D9" s="14">
+        <f t="shared" ref="D9:D11" si="0">B9*C9</f>
+        <v>1000000</v>
+      </c>
+      <c r="E9" s="6">
+        <f t="shared" ref="E9:E11" si="1">B9*C9*C9</f>
+        <v>2000000000000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1047,31 +1059,37 @@
       <c r="C10" s="13">
         <v>10000000</v>
       </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D10" s="14">
+        <f t="shared" si="0"/>
+        <v>2500000</v>
+      </c>
+      <c r="E10" s="6">
+        <f t="shared" si="1"/>
+        <v>25000000000000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.6">
       <c r="C11" t="s">
         <v>36</v>
       </c>
       <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
+      <c r="E11" s="6"/>
       <c r="F11" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.6">
       <c r="D12" s="16"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.6">
       <c r="D13" s="16"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -1088,7 +1106,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
@@ -1101,7 +1119,7 @@
       <c r="D17" s="14"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -1114,7 +1132,7 @@
       <c r="D18" s="14"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A19" s="1" t="s">
         <v>6</v>
       </c>
@@ -1127,7 +1145,7 @@
       <c r="D19" s="14"/>
       <c r="E19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.6">
       <c r="C20" t="s">
         <v>36</v>
       </c>
@@ -1137,10 +1155,10 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.6">
       <c r="D21" s="16"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.6">
       <c r="D22" s="16"/>
     </row>
   </sheetData>
@@ -1153,7 +1171,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B54E7F93-CF65-4DAA-B3EB-6DBD31CBAB62}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="3" max="3" width="16.125" customWidth="1"/>
     <col min="4" max="4" width="19.25" customWidth="1"/>
@@ -1161,7 +1179,7 @@
     <col min="6" max="6" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1175,7 +1193,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A2" s="11" t="s">
         <v>4</v>
       </c>
@@ -1189,7 +1207,7 @@
         <v>-1000000</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A3" s="11" t="s">
         <v>5</v>
       </c>
@@ -1203,7 +1221,7 @@
         <v>2500000</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A4" s="11" t="s">
         <v>6</v>
       </c>
@@ -1217,12 +1235,12 @@
         <v>5000000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -1239,7 +1257,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1256,7 +1274,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1273,7 +1291,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1290,7 +1308,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.6">
       <c r="C11" t="s">
         <v>36</v>
       </c>
@@ -1304,18 +1322,18 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.6">
       <c r="D12" s="15"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.6">
       <c r="D13" s="15"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -1332,7 +1350,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
@@ -1349,7 +1367,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -1366,7 +1384,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A19" s="1" t="s">
         <v>6</v>
       </c>
@@ -1383,7 +1401,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.6">
       <c r="C20" t="s">
         <v>36</v>
       </c>
@@ -1406,7 +1424,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{948DC152-A0E4-4F0A-AF32-70B901E1C395}">
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="3" max="3" width="16.125" customWidth="1"/>
     <col min="4" max="4" width="19.25" customWidth="1"/>
@@ -1414,7 +1432,7 @@
     <col min="6" max="6" width="13.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1428,7 +1446,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1442,7 +1460,7 @@
         <v>-2000000</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1456,7 +1474,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1470,12 +1488,12 @@
         <v>7000000</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -1492,7 +1510,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1505,7 +1523,7 @@
       <c r="D8" s="7"/>
       <c r="E8" s="5"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1519,7 +1537,7 @@
       <c r="E9" s="5"/>
       <c r="J9" s="10"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1532,7 +1550,7 @@
       <c r="D10" s="7"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.6">
       <c r="C11" t="s">
         <v>36</v>
       </c>
@@ -1542,18 +1560,18 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.6">
       <c r="D12" s="15"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.6">
       <c r="D13" s="15"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -1570,7 +1588,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
@@ -1583,7 +1601,7 @@
       <c r="D17" s="7"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -1596,7 +1614,7 @@
       <c r="D18" s="7"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A19" s="1" t="s">
         <v>6</v>
       </c>
@@ -1609,7 +1627,7 @@
       <c r="D19" s="7"/>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.6">
       <c r="C20" t="s">
         <v>36</v>
       </c>
@@ -1619,10 +1637,10 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.6">
       <c r="D21" s="15"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.6">
       <c r="D22" s="15"/>
     </row>
   </sheetData>
@@ -1635,7 +1653,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3661351A-B14A-435E-B895-7FEBFE7BB31A}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="3" max="3" width="16.125" customWidth="1"/>
     <col min="4" max="4" width="19.25" customWidth="1"/>
@@ -1643,7 +1661,7 @@
     <col min="6" max="6" width="11.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1657,7 +1675,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1671,7 +1689,7 @@
         <v>-2000000</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1685,7 +1703,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1699,12 +1717,12 @@
         <v>7000000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -1721,7 +1739,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1738,7 +1756,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1755,7 +1773,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1772,7 +1790,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.6">
       <c r="C11" t="s">
         <v>36</v>
       </c>
@@ -1786,18 +1804,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.6">
       <c r="D12" s="15"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.6">
       <c r="D13" s="15"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -1814,7 +1832,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
@@ -1831,7 +1849,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -1848,7 +1866,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A19" s="1" t="s">
         <v>6</v>
       </c>
@@ -1865,7 +1883,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.6">
       <c r="C20" t="s">
         <v>36</v>
       </c>
@@ -1879,10 +1897,10 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.6">
       <c r="D21" s="15"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.6">
       <c r="D22" s="15"/>
     </row>
   </sheetData>
